--- a/haustec_202606.xlsx
+++ b/haustec_202606.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\The-portal\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\KK445-PC\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4D458B99-FAA5-43D7-80B5-3E7E52D9B7E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0B19B398-0212-4D66-B834-BC734207B0EA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-2430" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="36" yWindow="756" windowWidth="23004" windowHeight="12204" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="202605" sheetId="1" r:id="rId1"/>
@@ -22,21 +22,13 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>出荷予定日</t>
-  </si>
-  <si>
     <t>納期</t>
-    <rPh sb="0" eb="2">
-      <t>ノウキ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
   </si>
   <si>
     <t>納入日</t>
-    <rPh sb="0" eb="3">
-      <t>ノウニュウビ</t>
-    </rPh>
-    <phoneticPr fontId="3"/>
+  </si>
+  <si>
+    <t>出荷予定日</t>
   </si>
 </sst>
 </file>
@@ -92,7 +84,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -115,22 +107,11 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFCCCCCC"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFCCCCCC"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -139,9 +120,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="14" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="14" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
   </cellXfs>
@@ -444,28 +422,6 @@
 </a:theme>
 </file>
 
-<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
-<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
-  <wetp:taskpane dockstate="right" visibility="0" width="350" row="7">
-    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
-  </wetp:taskpane>
-</wetp:taskpanes>
-</file>
-
-<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
-<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{B1373948-3E32-48A4-A58C-014B5BBAB399}">
-  <we:reference id="WA200009404" version="1.0.0.8" store="Omex" storeType="OMEX"/>
-  <we:alternateReferences>
-    <we:reference id="WA200009404" version="1.0.0.8" store="WA200009404" storeType="OMEX"/>
-  </we:alternateReferences>
-  <we:properties>
-    <we:property name="claude.fileId" value="&quot;5b0be894-7eba-4b7c-bfb2-2f5e2e5da2c2&quot;"/>
-  </we:properties>
-  <we:bindings/>
-  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
-</we:webextension>
-</file>
-
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C23"/>
@@ -476,250 +432,256 @@
   <sheetData>
     <row r="1" spans="1:3" ht="25.05" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>0</v>
       </c>
     </row>
     <row r="2" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A2" s="3">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="B2" s="3">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C2" s="3">
-        <v>46170</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="3" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A3" s="3">
-        <v>46175</v>
+        <v>46205</v>
       </c>
       <c r="B3" s="3">
-        <v>46174</v>
+        <v>46204</v>
       </c>
       <c r="C3" s="3">
-        <v>46170</v>
+        <v>46202</v>
       </c>
     </row>
     <row r="4" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A4" s="3">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="B4" s="3">
-        <v>46175</v>
+        <v>46205</v>
       </c>
       <c r="C4" s="3">
-        <v>46171</v>
+        <v>46203</v>
       </c>
     </row>
     <row r="5" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A5" s="3">
-        <v>46177</v>
+        <v>46209</v>
       </c>
       <c r="B5" s="3">
-        <v>46176</v>
+        <v>46206</v>
       </c>
       <c r="C5" s="3">
-        <v>46174</v>
+        <v>46204</v>
       </c>
     </row>
     <row r="6" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A6" s="3">
-        <v>46178</v>
+        <v>46210</v>
       </c>
       <c r="B6" s="3">
-        <v>46177</v>
+        <v>46209</v>
       </c>
       <c r="C6" s="3">
-        <v>46175</v>
+        <v>46205</v>
       </c>
     </row>
     <row r="7" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A7" s="3">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="B7" s="3">
-        <v>46178</v>
+        <v>46210</v>
       </c>
       <c r="C7" s="3">
-        <v>46176</v>
+        <v>46206</v>
       </c>
     </row>
     <row r="8" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A8" s="3">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="B8" s="3">
-        <v>46181</v>
+        <v>46211</v>
       </c>
       <c r="C8" s="3">
-        <v>46177</v>
+        <v>46209</v>
       </c>
     </row>
     <row r="9" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A9" s="3">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="B9" s="3">
-        <v>46182</v>
+        <v>46212</v>
       </c>
       <c r="C9" s="3">
-        <v>46178</v>
+        <v>46210</v>
       </c>
     </row>
     <row r="10" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A10" s="3">
-        <v>46184</v>
+        <v>46216</v>
       </c>
       <c r="B10" s="3">
-        <v>46183</v>
+        <v>46213</v>
       </c>
       <c r="C10" s="3">
-        <v>46181</v>
+        <v>46211</v>
       </c>
     </row>
     <row r="11" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
       <c r="A11" s="3">
-        <v>46185</v>
-      </c>
-      <c r="B11" s="4">
-        <v>46184</v>
+        <v>46217</v>
+      </c>
+      <c r="B11" s="3">
+        <v>46216</v>
       </c>
       <c r="C11" s="3">
-        <v>46182</v>
+        <v>46212</v>
       </c>
     </row>
     <row r="12" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A12" s="4">
-        <v>46188</v>
-      </c>
-      <c r="B12" s="4">
-        <v>46185</v>
+      <c r="A12" s="3">
+        <v>46218</v>
+      </c>
+      <c r="B12" s="3">
+        <v>46217</v>
       </c>
       <c r="C12" s="3">
-        <v>46183</v>
+        <v>46213</v>
       </c>
     </row>
     <row r="13" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A13" s="4">
-        <v>46189</v>
-      </c>
-      <c r="B13" s="4">
-        <v>46188</v>
+      <c r="A13" s="3">
+        <v>46219</v>
+      </c>
+      <c r="B13" s="3">
+        <v>46218</v>
       </c>
       <c r="C13" s="3">
-        <v>46184</v>
+        <v>46216</v>
       </c>
     </row>
     <row r="14" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A14" s="4">
-        <v>46190</v>
-      </c>
-      <c r="B14" s="4">
-        <v>46189</v>
+      <c r="A14" s="3">
+        <v>46220</v>
+      </c>
+      <c r="B14" s="3">
+        <v>46219</v>
       </c>
       <c r="C14" s="3">
-        <v>46185</v>
+        <v>46217</v>
       </c>
     </row>
     <row r="15" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A15" s="4">
-        <v>46191</v>
-      </c>
-      <c r="B15" s="4">
-        <v>46190</v>
+      <c r="A15" s="3">
+        <v>46224</v>
+      </c>
+      <c r="B15" s="3">
+        <v>46220</v>
       </c>
       <c r="C15" s="3">
-        <v>46188</v>
+        <v>46218</v>
       </c>
     </row>
     <row r="16" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A16" s="4">
-        <v>46192</v>
-      </c>
-      <c r="B16" s="4">
-        <v>46191</v>
+      <c r="A16" s="3">
+        <v>46225</v>
+      </c>
+      <c r="B16" s="3">
+        <v>46224</v>
       </c>
       <c r="C16" s="3">
-        <v>46189</v>
+        <v>46219</v>
       </c>
     </row>
     <row r="17" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A17" s="4">
-        <v>46195</v>
-      </c>
-      <c r="B17" s="4">
-        <v>46192</v>
+      <c r="A17" s="3">
+        <v>46226</v>
+      </c>
+      <c r="B17" s="3">
+        <v>46225</v>
       </c>
       <c r="C17" s="3">
-        <v>46190</v>
+        <v>46220</v>
       </c>
     </row>
     <row r="18" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A18" s="4">
-        <v>46196</v>
-      </c>
-      <c r="B18" s="4">
-        <v>46195</v>
+      <c r="A18" s="3">
+        <v>46227</v>
+      </c>
+      <c r="B18" s="3">
+        <v>46226</v>
       </c>
       <c r="C18" s="3">
-        <v>46191</v>
+        <v>46224</v>
       </c>
     </row>
     <row r="19" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A19" s="4">
-        <v>46197</v>
-      </c>
-      <c r="B19" s="4">
-        <v>46196</v>
+      <c r="A19" s="3">
+        <v>46230</v>
+      </c>
+      <c r="B19" s="3">
+        <v>46227</v>
       </c>
       <c r="C19" s="3">
-        <v>46192</v>
+        <v>46225</v>
       </c>
     </row>
     <row r="20" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A20" s="4">
-        <v>46198</v>
-      </c>
-      <c r="B20" s="4">
-        <v>46197</v>
+      <c r="A20" s="3">
+        <v>46231</v>
+      </c>
+      <c r="B20" s="3">
+        <v>46230</v>
       </c>
       <c r="C20" s="3">
-        <v>46195</v>
+        <v>46226</v>
       </c>
     </row>
     <row r="21" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A21" s="4">
-        <v>46199</v>
-      </c>
-      <c r="B21" s="4">
-        <v>46198</v>
+      <c r="A21" s="3">
+        <v>46232</v>
+      </c>
+      <c r="B21" s="3">
+        <v>46231</v>
       </c>
       <c r="C21" s="3">
-        <v>46196</v>
+        <v>46227</v>
       </c>
     </row>
     <row r="22" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A22" s="4">
-        <v>46202</v>
-      </c>
-      <c r="B22" s="4">
-        <v>46199</v>
+      <c r="A22" s="3">
+        <v>46233</v>
+      </c>
+      <c r="B22" s="3">
+        <v>46232</v>
       </c>
       <c r="C22" s="3">
-        <v>46197</v>
+        <v>46230</v>
       </c>
     </row>
     <row r="23" spans="1:3" ht="13.8" x14ac:dyDescent="0.25">
-      <c r="A23" s="4"/>
-      <c r="B23" s="4"/>
-      <c r="C23" s="3"/>
+      <c r="A23" s="3">
+        <v>46234</v>
+      </c>
+      <c r="B23" s="3">
+        <v>46233</v>
+      </c>
+      <c r="C23" s="3">
+        <v>46231</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3"/>
